--- a/docs/WFMHub Report Design Reference.xlsx
+++ b/docs/WFMHub Report Design Reference.xlsx
@@ -190,7 +190,7 @@
     <t>UPDATED</t>
   </si>
   <si>
-    <t>WFMHUB-DESIGN 3.2.0 · approved visual contract</t>
+    <t>WFMHUB-DESIGN 3.4.0 · approved visual contract</t>
   </si>
   <si>
     <t>TOKENS</t>
